--- a/docentes/Silva Villegas Mario - Estadisticos 20211.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20211.xlsx
@@ -673,7 +673,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20211.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20211.xlsx
@@ -474,19 +474,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>57.58</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -539,16 +539,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E2">
+        <v>14</v>
+      </c>
+      <c r="F2">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>57.58</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -601,10 +604,10 @@
         <v>33</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>14</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -613,7 +616,7 @@
         <v>57.58</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20211.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20211.xlsx
@@ -67,13 +67,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
   </si>
 </sst>
 </file>
@@ -539,7 +539,7 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>14</v>
@@ -551,7 +551,7 @@
         <v>57.58</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -607,16 +607,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>57.58</v>
+        <v>69.7</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +658,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -676,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
